--- a/public/certificate/battle arena.xlsx
+++ b/public/certificate/battle arena.xlsx
@@ -1549,7 +1549,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1563,7 +1563,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1577,7 +1577,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1591,7 +1591,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1605,7 +1605,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1619,7 +1619,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1633,7 +1633,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1647,7 +1647,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1661,7 +1661,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1675,7 +1675,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1689,7 +1689,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1703,7 +1703,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1717,7 +1717,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1731,7 +1731,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1745,7 +1745,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1759,7 +1759,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1773,7 +1773,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1802,7 +1802,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1">
-    <tableStyle name="Sheet1-style" pivot="0" count="2" xr9:uid="{1D841F3F-D8E2-4E48-BB99-BE7E61D06EDC}">
+    <tableStyle name="Sheet1-style" pivot="0" count="2" xr9:uid="{2241B911-A667-4E90-AA71-EEC581986C6D}">
       <tableStyleElement type="firstRowStripe" dxfId="18"/>
       <tableStyleElement type="secondRowStripe" dxfId="17"/>
     </tableStyle>
@@ -2848,7 +2848,7 @@
       <c r="A17" s="5">
         <v>46120.5653324768</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="B17" s="9" t="s">
         <v>136</v>
       </c>
       <c r="C17" s="7" t="s">
@@ -3350,6 +3350,7 @@
     <hyperlink ref="B3" r:id="rId26" display="suryanshpatels143@gmail.com" tooltip="mailto:suryanshpatels143@gmail.com"/>
     <hyperlink ref="B8" r:id="rId27" display="aryan1btech24-28@liet.in"/>
     <hyperlink ref="B9" r:id="rId28" display="piyushsinghbtech24-28@liet.in"/>
+    <hyperlink ref="B17" r:id="rId29" display="aditya8459343180@gmail.com"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
